--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20211.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -76,76 +76,67 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>APONTE</t>
   </si>
   <si>
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>VENEGAS</t>
   </si>
   <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>APONTE</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>ANETTE JOCELYN</t>
+  </si>
+  <si>
+    <t>ADAL</t>
+  </si>
+  <si>
+    <t>MIXTLI TONATI</t>
+  </si>
+  <si>
+    <t>NATALIA</t>
   </si>
   <si>
     <t>BRYAN ABRAHAM</t>
   </si>
   <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>NANCY PAOLA</t>
-  </si>
-  <si>
-    <t>ANETTE JOCELYN</t>
-  </si>
-  <si>
     <t>ANDRIK YOSIMAR</t>
-  </si>
-  <si>
-    <t>MIXTLI TONATI</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
   </si>
 </sst>
 </file>
@@ -546,10 +537,10 @@
         <v>36</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>5</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
       </c>
       <c r="F2">
         <v>31</v>
@@ -558,7 +549,7 @@
         <v>86.11</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -572,19 +563,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>67.44</v>
+        <v>72.09</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -598,19 +589,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>83.72</v>
+        <v>88.37</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -624,10 +615,10 @@
         <v>24</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>2</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
       </c>
       <c r="F5">
         <v>22</v>
@@ -636,7 +627,7 @@
         <v>91.67</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -689,16 +680,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -712,16 +706,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>62.79</v>
+      </c>
+      <c r="H3">
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -735,16 +732,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>69.77</v>
+      </c>
+      <c r="H4">
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -758,16 +758,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>79.17</v>
+      </c>
+      <c r="H5">
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -820,10 +823,10 @@
         <v>36</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>5</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
       </c>
       <c r="F2">
         <v>31</v>
@@ -846,19 +849,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>67.44</v>
+        <v>72.09</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -872,16 +875,16 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>83.72</v>
+        <v>88.37</v>
       </c>
       <c r="H4">
         <v>6.8</v>
@@ -898,10 +901,10 @@
         <v>24</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>2</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
       </c>
       <c r="F5">
         <v>22</v>
@@ -910,7 +913,7 @@
         <v>91.67</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -920,7 +923,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -952,16 +955,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920277</v>
+        <v>21330051920284</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -970,168 +973,145 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920284</v>
+        <v>21330051920306</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920288</v>
+        <v>21330051920309</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920306</v>
+        <v>21330051920225</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920324</v>
+        <v>21330051920271</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920225</v>
+        <v>21330051920277</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920271</v>
+        <v>21330051920324</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920305</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20211.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20211.xlsx
@@ -973,7 +973,7 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -996,7 +996,7 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1019,7 +1019,7 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1042,7 +1042,7 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1065,7 +1065,7 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1088,7 +1088,7 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1111,7 +1111,7 @@
         <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20211.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20211.xlsx
@@ -1088,7 +1088,7 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">

--- a/docentes/González Altamirano Victorino Juventino - Estadisticos 20211.xlsx
+++ b/docentes/González Altamirano Victorino Juventino - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="57">
   <si>
     <t>Mat</t>
   </si>
@@ -76,67 +76,118 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
   </si>
   <si>
     <t>MONTALVO</t>
   </si>
   <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>MATLATECATL</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
+    <t>VENEGAS</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>ABAD</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
   </si>
   <si>
     <t>PANZO</t>
   </si>
   <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
     <t>ESPINOSA</t>
   </si>
   <si>
-    <t>APONTE</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>ANETTE JOCELYN</t>
+    <t>AMECA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>EDNA</t>
+  </si>
+  <si>
+    <t>DARLA MARLENE</t>
   </si>
   <si>
     <t>ADAL</t>
   </si>
   <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>DULCE DANIELA</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
     <t>MIXTLI TONATI</t>
   </si>
   <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>BRYAN ABRAHAM</t>
-  </si>
-  <si>
-    <t>ANDRIK YOSIMAR</t>
+    <t>EZEQUIEL</t>
+  </si>
+  <si>
+    <t>PERLA</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
   </si>
 </sst>
 </file>
@@ -563,10 +614,10 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3">
         <v>31</v>
@@ -680,19 +731,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -706,19 +757,19 @@
         <v>43</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>13</v>
       </c>
-      <c r="E3">
-        <v>15</v>
-      </c>
       <c r="F3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>62.79</v>
+        <v>69.77</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -732,19 +783,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>69.77</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -758,19 +809,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>79.17</v>
+        <v>87.5</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -826,16 +877,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>86.11</v>
+        <v>75</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -849,19 +900,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>72.09</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -878,16 +929,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>88.37</v>
+        <v>74.42</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -913,7 +964,7 @@
         <v>91.67</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -923,7 +974,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -955,22 +1006,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920284</v>
+        <v>21330051920235</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -978,39 +1029,39 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920306</v>
+        <v>21330051920242</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920309</v>
+        <v>21330051920289</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1024,22 +1075,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920225</v>
+        <v>21330051920297</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1047,70 +1098,208 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920271</v>
+        <v>21330051920304</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920277</v>
+        <v>21330051920309</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920324</v>
+        <v>21330051920353</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920240</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920249</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
         <v>39</v>
       </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920225</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920287</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920295</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
         <v>11</v>
       </c>
-      <c r="G8">
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920331</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14">
         <v>1</v>
       </c>
     </row>
